--- a/Results/TestCases/XLSX/validations_TestCases.xlsx
+++ b/Results/TestCases/XLSX/validations_TestCases.xlsx
@@ -72,7 +72,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>SKIPPED</t>
+    <t>PASSED</t>
   </si>
   <si>
     <t>TC_VALID_02</t>
@@ -249,7 +249,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF5A6268"/>
+      <color rgb="FF107C41"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
@@ -268,7 +268,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E3E5"/>
+        <fgColor rgb="FFD1E7DD"/>
       </patternFill>
     </fill>
   </fills>

--- a/Results/TestCases/XLSX/validations_TestCases.xlsx
+++ b/Results/TestCases/XLSX/validations_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="101">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -58,15 +58,14 @@
     <t>Positive</t>
   </si>
   <si>
-    <t>OrangeHRM application is accessible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to page
-2. Perform test actions
-3. Verify assertions</t>
-  </si>
-  <si>
-    <t>Test executes successfully and all assertions pass</t>
+    <t>The OrangeHRM login page is loaded in the browser.</t>
+  </si>
+  <si>
+    <t>1. Click the Login button without entering any credentials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The username error should equal 'Required'
+- The password error should equal 'Required'</t>
   </si>
   <si>
     <t>High</t>
@@ -81,18 +80,36 @@
     <t>Verify validation when only password is entered</t>
   </si>
   <si>
+    <t>1. Enter only the password and click the Login button</t>
+  </si>
+  <si>
+    <t>- The username error should equal 'Required'</t>
+  </si>
+  <si>
     <t>TC_VALID_03</t>
   </si>
   <si>
     <t>Verify validation when only username is entered</t>
   </si>
   <si>
+    <t>1. Enter only the username and click the Login button</t>
+  </si>
+  <si>
+    <t>- The password error should equal 'Required'</t>
+  </si>
+  <si>
     <t>TC_VALID_04</t>
   </si>
   <si>
     <t>Verify login fails with special characters in credentials</t>
   </si>
   <si>
+    <t>1. Enter the username and password, then click the Login button</t>
+  </si>
+  <si>
+    <t>- The error text should equal 'Invalid credentials'</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -105,6 +122,9 @@
     <t>Negative</t>
   </si>
   <si>
+    <t>- The error text || 'invalid credentials' should be present</t>
+  </si>
+  <si>
     <t>TC_VALID_06</t>
   </si>
   <si>
@@ -129,12 +149,21 @@
     <t>Verify error validation text elements have correct text color (red)</t>
   </si>
   <si>
+    <t>- The color should contain 'rgb(235, 9, 16)'</t>
+  </si>
+  <si>
     <t>TC_VALID_10</t>
   </si>
   <si>
     <t>Verify username field does not exceed max length limit of HTML standards</t>
   </si>
   <si>
+    <t>1. Perform the actions described in the test title</t>
+  </si>
+  <si>
+    <t>- The maxlen should be null</t>
+  </si>
+  <si>
     <t>TC_VALID_11</t>
   </si>
   <si>
@@ -147,18 +176,27 @@
     <t>Verify error message font weight is responsive</t>
   </si>
   <si>
+    <t>- The weight should be present</t>
+  </si>
+  <si>
     <t>TC_VALID_13</t>
   </si>
   <si>
     <t>Verify input error borders are styled on required error trigger</t>
   </si>
   <si>
+    <t>- The border should be present</t>
+  </si>
+  <si>
     <t>TC_VALID_14</t>
   </si>
   <si>
     <t>Verify form submits only when all validation requirements are met</t>
   </si>
   <si>
+    <t>- The form element should be present</t>
+  </si>
+  <si>
     <t>TC_VALID_15</t>
   </si>
   <si>
@@ -177,52 +215,107 @@
     <t>Verify error alert has company icon or style container</t>
   </si>
   <si>
+    <t>- The error alert message should be visible</t>
+  </si>
+  <si>
     <t>TC_VALID_18</t>
   </si>
   <si>
     <t>Verify login page form submission tag exists</t>
   </si>
   <si>
+    <t>- The oxd form element should be visible</t>
+  </si>
+  <si>
     <t>TC_VALID_19</t>
   </si>
   <si>
     <t>Verify login button is of type submit</t>
   </si>
   <si>
+    <t>- The type should equal 'submit'</t>
+  </si>
+  <si>
     <t>TC_VALID_20</t>
   </si>
   <si>
     <t>Verify field label tags are capitalized</t>
   </si>
   <si>
+    <t>- The 'Username' element should be visible</t>
+  </si>
+  <si>
     <t>TC_VALID_21</t>
   </si>
   <si>
     <t>Verify password input field has password autocomplete settings</t>
   </si>
   <si>
+    <t>- The type should equal 'password'</t>
+  </si>
+  <si>
     <t>TC_VALID_22</t>
   </si>
   <si>
     <t>Verify spacing styles around form input groupings</t>
   </si>
   <si>
+    <t>- The group should be visible</t>
+  </si>
+  <si>
     <t>TC_VALID_23</t>
   </si>
   <si>
     <t>Verify login button displays hover class transitions</t>
   </si>
   <si>
+    <t>- The cursor should equal 'pointer'</t>
+  </si>
+  <si>
     <t>TC_VALID_24</t>
   </si>
   <si>
     <t>Verify HTML lang details exist on login viewport</t>
   </si>
   <si>
+    <t>- The lang === null || lang === 'en' should equal 'true'</t>
+  </si>
+  <si>
     <t>TC_VALID_25</t>
   </si>
   <si>
     <t>Verify validation on long username does not crash backend</t>
+  </si>
+  <si>
+    <t>TC_VALID_26</t>
+  </si>
+  <si>
+    <t>Verify login fails safely with an XSS script payload in the password field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The error text should equal 'Invalid credentials'
+- The dialog fired should equal 'false'</t>
+  </si>
+  <si>
+    <t>TC_VALID_27</t>
+  </si>
+  <si>
+    <t>Verify login fails with unicode and emoji characters in the username</t>
+  </si>
+  <si>
+    <t>- The ['invalid credentials', 'unexpected error occurred'] should contain 'errorText'</t>
+  </si>
+  <si>
+    <t>TC_VALID_28</t>
+  </si>
+  <si>
+    <t>Verify login fails when username contains only control/whitespace characters</t>
+  </si>
+  <si>
+    <t>TC_VALID_29</t>
+  </si>
+  <si>
+    <t>Verify login fails with an extremely long password without a server error</t>
   </si>
 </sst>
 </file>
@@ -660,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -766,10 +859,10 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -780,7 +873,7 @@
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -789,22 +882,22 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -815,7 +908,7 @@
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -824,25 +917,25 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>19</v>
@@ -850,7 +943,7 @@
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -859,25 +952,25 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>19</v>
@@ -885,34 +978,34 @@
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>19</v>
@@ -920,7 +1013,7 @@
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -929,25 +1022,25 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>19</v>
@@ -955,7 +1048,7 @@
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -964,25 +1057,25 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>19</v>
@@ -990,7 +1083,7 @@
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -999,13 +1092,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -1014,10 +1107,10 @@
         <v>16</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>19</v>
@@ -1025,7 +1118,7 @@
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1034,25 +1127,25 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>19</v>
@@ -1060,7 +1153,7 @@
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1069,25 +1162,25 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>19</v>
@@ -1095,7 +1188,7 @@
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1104,13 +1197,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -1119,10 +1212,10 @@
         <v>16</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>19</v>
@@ -1130,7 +1223,7 @@
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1139,13 +1232,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -1154,10 +1247,10 @@
         <v>16</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>19</v>
@@ -1165,7 +1258,7 @@
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1174,25 +1267,25 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>19</v>
@@ -1200,7 +1293,7 @@
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1209,25 +1302,25 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>19</v>
@@ -1235,7 +1328,7 @@
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1244,25 +1337,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>19</v>
@@ -1270,7 +1363,7 @@
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1279,25 +1372,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>19</v>
@@ -1305,7 +1398,7 @@
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1314,25 +1407,25 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>19</v>
@@ -1340,7 +1433,7 @@
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1349,25 +1442,25 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>19</v>
@@ -1375,7 +1468,7 @@
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1384,25 +1477,25 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>19</v>
@@ -1410,7 +1503,7 @@
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1419,25 +1512,25 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>19</v>
@@ -1445,7 +1538,7 @@
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1454,25 +1547,25 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>19</v>
@@ -1480,7 +1573,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1489,25 +1582,25 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>19</v>
@@ -1515,7 +1608,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1524,25 +1617,25 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>19</v>
@@ -1550,7 +1643,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1559,27 +1652,167 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K26" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>19</v>
       </c>
     </row>
